--- a/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.05 Boyama Laboratuvarı Daldırma Formu.xlsx
+++ b/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.05 Boyama Laboratuvarı Daldırma Formu.xlsx
@@ -172,7 +172,7 @@
     <t>ONAYLAYAN</t>
   </si>
   <si>
-    <t>EG.QA.FRM.04.07</t>
+    <t>EMS.QA.FRM.04.07</t>
   </si>
   <si>
     <t>Style الموديل</t>
@@ -191,7 +191,7 @@
 عينات أختبار الصبغة</t>
   </si>
   <si>
-    <t>EG.WS.RPR.04.05</t>
+    <t>EMS.WS.RPR.04.05</t>
   </si>
   <si>
     <t>Stil Adı:</t>

--- a/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.05 Boyama Laboratuvarı Daldırma Formu.xlsx
+++ b/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.05 Boyama Laboratuvarı Daldırma Formu.xlsx
@@ -4110,8 +4110,10 @@
       <c r="X2" s="82"/>
       <c r="Y2" s="82"/>
       <c r="Z2" s="83"/>
-      <c r="AA2" s="94" t="s">
-        <v>34</v>
+      <c r="AA2" s="94" t="inlineStr">
+        <is>
+          <t>EMS.WS.RPR.04.05</t>
+        </is>
       </c>
       <c r="AB2" s="95"/>
       <c r="AC2" s="95"/>
